--- a/Flag/Extrair DP/Planilha_DESFLAG.xlsx
+++ b/Flag/Extrair DP/Planilha_DESFLAG.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,70 +441,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Anticoagulante Seguro</t>
+          <t>Cuidado Integral da Mama</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>089181160</t>
+          <t>094992152</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anticoagulante Seguro</t>
+          <t>Cuidado Oncológico Pulmonar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>079819936</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Anticoagulante Seguro</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>094079415</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Anticoagulante Seguro</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>094956702</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Anticoagulante Seguro</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>084691196</t>
+          <t>089933823</t>
         </is>
       </c>
     </row>
